--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_DM GROUP MOLLET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_DM GROUP MOLLET.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>162.2</v>
+        <v>399.04</v>
       </c>
       <c r="C2" t="n">
-        <v>162.34</v>
+        <v>397.98</v>
       </c>
       <c r="D2" t="n">
-        <v>115.1903412590859</v>
+        <v>104.2765968139102</v>
       </c>
       <c r="E2" t="n">
-        <v>101.6385364050758</v>
+        <v>102.0151766420423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5465116279069767</v>
+        <v>0.4890965732087227</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1637554585152839</v>
+        <v>0.160073677747566</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2837837837837838</v>
+        <v>0.2893401015228426</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3565891472868217</v>
+        <v>0.3146417445482866</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="M2" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="N2" t="n">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="O2" t="n">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5658914728682171</v>
+        <v>0.5856697819314641</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="S2" t="n">
-        <v>0.04651162790697674</v>
+        <v>0.04361370716510903</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0310077519379845</v>
+        <v>0.01557632398753894</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1162790697674419</v>
+        <v>0.1370716510903427</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2403100775193799</v>
+        <v>0.2180685358255452</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5342465753424658</v>
+        <v>0.5425531914893617</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.068493150684932</v>
+        <v>1.085106382978723</v>
       </c>
       <c r="AI2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>1.239130434782609</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.6206896551724138</v>
-      </c>
       <c r="AL2" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5964912280701754</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.1</v>
+        <v>1.10958904109589</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.3</v>
+        <v>4.397260273972603</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.4</v>
+        <v>5.506849315068493</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.09999999999999</v>
+        <v>79.80799999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>81.17</v>
+        <v>79.596</v>
       </c>
       <c r="D3" t="n">
-        <v>115.1903412590859</v>
+        <v>104.2765968139102</v>
       </c>
       <c r="E3" t="n">
-        <v>101.6385364050758</v>
+        <v>102.0151766420423</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5465116279069767</v>
+        <v>0.4890965732087227</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1637554585152839</v>
+        <v>0.160073677747566</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2837837837837838</v>
+        <v>0.2893401015228427</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3565891472868217</v>
+        <v>0.3146417445482866</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="L3" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="M3" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>19.5</v>
+        <v>20.4</v>
       </c>
       <c r="O3" t="n">
-        <v>36.5</v>
+        <v>37.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5658914728682171</v>
+        <v>0.5856697819314641</v>
       </c>
       <c r="Q3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.04361370716510903</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.04651162790697674</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
+        <v>0.01557632398753894</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1370716510903427</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2180685358255452</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5425531914893617</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.085106382978723</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.8947368421052633</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.5</v>
       </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.0310077519379845</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.1162790697674419</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.2403100775193799</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.5342465753424658</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.4516129032258064</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.068493150684932</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.239130434782609</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.6206896551724138</v>
-      </c>
       <c r="AL3" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5964912280701754</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.1</v>
+        <v>1.10958904109589</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.3</v>
+        <v>4.397260273972603</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>5.506849315068494</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>162.48</v>
+        <v>396.92</v>
       </c>
       <c r="C4" t="n">
-        <v>162.34</v>
+        <v>397.98</v>
       </c>
       <c r="D4" t="n">
-        <v>101.6385364050758</v>
+        <v>102.0151766420423</v>
       </c>
       <c r="E4" t="n">
-        <v>115.1903412590859</v>
+        <v>104.2765968139102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4563492063492063</v>
+        <v>0.4541284403669725</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1571986123156982</v>
+        <v>0.1772451046590142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.282051282051282</v>
+        <v>0.3632075471698113</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3968253968253968</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J4" t="n">
+        <v>46</v>
+      </c>
+      <c r="K4" t="n">
+        <v>46</v>
+      </c>
+      <c r="L4" t="n">
+        <v>71</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32</v>
+      </c>
+      <c r="N4" t="n">
+        <v>67</v>
+      </c>
+      <c r="O4" t="n">
+        <v>136</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4159021406727829</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>21</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.06422018348623854</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" t="n">
         <v>27</v>
       </c>
-      <c r="K4" t="n">
-        <v>23</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26</v>
-      </c>
-      <c r="M4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" t="n">
-        <v>27</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="V4" t="n">
+        <v>0.08256880733944955</v>
+      </c>
+      <c r="W4" t="n">
+        <v>12</v>
+      </c>
+      <c r="X4" t="n">
         <v>51</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.4047619047619048</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="T4" t="n">
-        <v>7</v>
-      </c>
-      <c r="U4" t="n">
-        <v>13</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1031746031746032</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>23</v>
-      </c>
       <c r="Y4" t="n">
-        <v>0.1825396825396825</v>
+        <v>0.1559633027522936</v>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.253968253968254</v>
+        <v>0.2813455657492355</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.4926470588235294</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3125</v>
+        <v>0.3152173913043478</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.058823529411765</v>
+        <v>0.9852941176470589</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.076923076923077</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8601398601398601</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9</v>
+        <v>0.6301369863013698</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.045454545454545</v>
+        <v>0.5974025974025974</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.733333333333333</v>
+        <v>1.69047619047619</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9880952380952381</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.344827586206897</v>
+        <v>3.892857142857143</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.310344827586207</v>
+        <v>4.880952380952381</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.24000000000001</v>
+        <v>79.384</v>
       </c>
       <c r="C5" t="n">
-        <v>81.17</v>
+        <v>79.596</v>
       </c>
       <c r="D5" t="n">
-        <v>101.6385364050758</v>
+        <v>102.0151766420423</v>
       </c>
       <c r="E5" t="n">
-        <v>115.1903412590859</v>
+        <v>104.2765968139102</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4563492063492063</v>
+        <v>0.4541284403669724</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1571986123156982</v>
+        <v>0.1772451046590142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.282051282051282</v>
+        <v>0.3632075471698114</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3968253968253968</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="N5" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="O5" t="n">
-        <v>25.5</v>
+        <v>27.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.4159021406727828</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.06422018348623854</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1031746031746032</v>
+        <v>0.08256880733944955</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>10.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1825396825396825</v>
+        <v>0.1559633027522936</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.253968253968254</v>
+        <v>0.2813455657492354</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.4926470588235294</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3125</v>
+        <v>0.3152173913043478</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.058823529411765</v>
+        <v>0.9852941176470589</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.076923076923077</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8601398601398601</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9</v>
+        <v>0.6301369863013698</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.045454545454545</v>
+        <v>0.5974025974025974</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.733333333333333</v>
+        <v>1.69047619047619</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9880952380952381</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.344827586206897</v>
+        <v>3.892857142857143</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.310344827586207</v>
+        <v>4.88095238095238</v>
       </c>
     </row>
     <row r="7">
@@ -1594,82 +1594,82 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>84</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>36</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0.792</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1690,66 +1690,66 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>62:08</t>
+          <t>144:48</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>23.64</v>
+        <v>65.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.789</v>
+        <v>0.68</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.832</v>
+        <v>0.714</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.523</v>
+        <v>1.277</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.316</v>
+        <v>0.32</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>1.571</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.5</v>
+        <v>7.143</v>
       </c>
       <c r="AW9" t="n">
-        <v>11.5</v>
+        <v>8.714</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.166</v>
+        <v>0.199</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.149</v>
+        <v>0.13</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.082</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="10">
@@ -1759,64 +1759,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
-        <v>6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1828,22 +1828,22 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5</v>
+        <v>0.409</v>
       </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -1858,63 +1858,63 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>55:29</t>
+          <t>121:52</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>27.76</v>
+        <v>50.52</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.556</v>
+        <v>0.431</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.607</v>
+        <v>0.493</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.865</v>
+        <v>0.772</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.288</v>
+        <v>0.218</v>
       </c>
       <c r="AT10" t="n">
         <v>0.222</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.75</v>
+        <v>1.727</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.25</v>
+        <v>3.273</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.218</v>
+        <v>0.182</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.019</v>
+        <v>0.042</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.037</v>
+        <v>0.062</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.115</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="11">
@@ -1924,88 +1924,88 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>48</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>37</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" t="n">
+        <v>31</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
-        <v>24</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="n">
+      <c r="R11" t="n">
+        <v>16</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>31</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" t="n">
         <v>10</v>
       </c>
-      <c r="I11" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="X11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>16</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2032,54 +2032,54 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>42:24</t>
+          <t>93:15</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>30.16</v>
+        <v>61.64</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.333</v>
+        <v>0.349</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.442</v>
+        <v>0.424</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.796</v>
+        <v>0.779</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.099</v>
+        <v>0.081</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.476</v>
+        <v>0.419</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.311</v>
+        <v>0.29</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.076</v>
+        <v>0.109</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.266</v>
+        <v>0.212</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.111</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="12">
@@ -2089,82 +2089,82 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
+        <v>9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>33</v>
+      </c>
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>19</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2197,54 +2197,54 @@
         <v>1</v>
       </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31:03</t>
+          <t>83:31</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>28.88</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.542</v>
+        <v>0.523</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.542</v>
+        <v>0.524</v>
       </c>
       <c r="AR12" t="n">
-        <v>1</v>
+        <v>0.831</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.077</v>
+        <v>0.208</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>3.667</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>4.167</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.183</v>
+        <v>0.152</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.209</v>
+        <v>0.17</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.264</v>
+        <v>0.181</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="13">
@@ -2254,106 +2254,106 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>17</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="N13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
         <v>4</v>
       </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2369,47 +2369,47 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38:03</t>
+          <t>101:28</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>10.44</v>
+        <v>31.96</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.375</v>
+        <v>0.522</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.415</v>
+        <v>0.575</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.67</v>
+        <v>0.97</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.192</v>
+        <v>0.156</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.125</v>
+        <v>0.304</v>
       </c>
       <c r="AU13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.12</v>
+        <v>0.138</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.162</v>
+        <v>0.158</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2419,162 +2419,162 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>28</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>13</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>20</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" t="n">
         <v>2</v>
       </c>
-      <c r="C14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="Y14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
       <c r="AL14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26:53</t>
+          <t>87:13</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>7.76</v>
+        <v>29.2</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.167</v>
+        <v>0.575</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.155</v>
+        <v>0.631</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.418</v>
+        <v>0.959</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.387</v>
+        <v>0.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.333</v>
+        <v>0.25</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>2.857</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.333</v>
+        <v>3.286</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.126</v>
+        <v>0.147</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.038</v>
+        <v>0.119</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="15">
@@ -2584,40 +2584,40 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="n">
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
         <v>13</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2626,19 +2626,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2683,63 +2683,63 @@
         <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AM15" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>53:31</t>
+        </is>
+      </c>
+      <c r="AO15" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AP15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>22:15</t>
-        </is>
-      </c>
-      <c r="AO15" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.857</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>0.874</v>
+        <v>0.523</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.245</v>
+        <v>0.849</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.287</v>
+        <v>0.189</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.143</v>
+        <v>0.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.333</v>
+        <v>3.75</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.667</v>
+        <v>4.25</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.205</v>
+        <v>0.174</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.049</v>
+        <v>0.019</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="16">
@@ -2749,40 +2749,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
@@ -2791,49 +2791,49 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="X16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
+      <c r="Y16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2857,54 +2857,54 @@
         <v>1</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>76:00</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>8.880000000000001</v>
+        <v>30.52</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5</v>
+        <v>0.395</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.444</v>
+        <v>0.422</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.788</v>
+        <v>0.623</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.113</v>
+        <v>0.262</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="AU16" t="n">
-        <v>4</v>
+        <v>1.125</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>2.375</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.168</v>
+        <v>0.176</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.044</v>
+        <v>0.074</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="17">
@@ -2914,40 +2914,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" t="n">
+        <v>18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>28</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
         <v>9</v>
       </c>
-      <c r="H17" t="n">
-        <v>12</v>
-      </c>
-      <c r="I17" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5</v>
-      </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -2956,120 +2956,120 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
+        <v>22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>22</v>
+      </c>
+      <c r="U17" t="n">
+        <v>9</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL17" t="n">
         <v>9</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>14</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>4</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>4</v>
-      </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>50:09</t>
+          <t>117:01</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>28.16</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.316</v>
+        <v>0.385</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.477</v>
+        <v>0.456</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.852</v>
+        <v>0.782</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.107</v>
+        <v>0.142</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.632</v>
+        <v>0.375</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.333</v>
+        <v>4.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.333</v>
+        <v>5.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.245</v>
+        <v>0.264</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.043</v>
+        <v>0.061</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.102</v>
+        <v>0.073</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="18">
@@ -3244,91 +3244,91 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="D19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I19" t="n">
+        <v>25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q19" t="n">
         <v>7</v>
       </c>
-      <c r="E19" t="n">
-        <v>12</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="R19" t="n">
+        <v>17</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>54</v>
+      </c>
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="H19" t="n">
+      <c r="V19" t="n">
         <v>8</v>
       </c>
-      <c r="I19" t="n">
-        <v>9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
+        <v>8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z19" t="n">
         <v>25</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>10</v>
-      </c>
       <c r="AA19" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="AB19" t="n">
         <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3343,63 +3343,63 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AM19" t="n">
-        <v>1</v>
+        <v>0.364</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48:30</t>
+          <t>121:21</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>22.96</v>
+        <v>64</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.667</v>
+        <v>0.533</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.738</v>
+        <v>0.616</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.22</v>
+        <v>1.078</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.174</v>
+        <v>0.125</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.533</v>
+        <v>0.467</v>
       </c>
       <c r="AU19" t="n">
         <v>0.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.75</v>
+        <v>5.625</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.5</v>
+        <v>6.375</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.207</v>
+        <v>0.231</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.19</v>
+        <v>0.117</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.058</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="20">
@@ -3409,52 +3409,52 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>2</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="Q20" t="n">
         <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3574,159 +3574,159 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>187</v>
+        <v>415</v>
       </c>
       <c r="D21" t="n">
+        <v>106</v>
+      </c>
+      <c r="E21" t="n">
+        <v>207</v>
+      </c>
+      <c r="F21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G21" t="n">
+        <v>114</v>
+      </c>
+      <c r="H21" t="n">
+        <v>101</v>
+      </c>
+      <c r="I21" t="n">
+        <v>141</v>
+      </c>
+      <c r="J21" t="n">
+        <v>81</v>
+      </c>
+      <c r="K21" t="n">
+        <v>135</v>
+      </c>
+      <c r="L21" t="n">
+        <v>57</v>
+      </c>
+      <c r="M21" t="n">
+        <v>52</v>
+      </c>
+      <c r="N21" t="n">
+        <v>18</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>35</v>
+      </c>
+      <c r="R21" t="n">
+        <v>118</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>326</v>
+      </c>
+      <c r="U21" t="n">
         <v>42</v>
       </c>
-      <c r="E21" t="n">
-        <v>83</v>
-      </c>
-      <c r="F21" t="n">
-        <v>19</v>
-      </c>
-      <c r="G21" t="n">
-        <v>46</v>
-      </c>
-      <c r="H21" t="n">
-        <v>46</v>
-      </c>
-      <c r="I21" t="n">
-        <v>55</v>
-      </c>
-      <c r="J21" t="n">
-        <v>33</v>
-      </c>
-      <c r="K21" t="n">
-        <v>56</v>
-      </c>
-      <c r="L21" t="n">
-        <v>21</v>
-      </c>
-      <c r="M21" t="n">
-        <v>19</v>
-      </c>
-      <c r="N21" t="n">
-        <v>9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>17</v>
-      </c>
-      <c r="R21" t="n">
-        <v>51</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>156</v>
-      </c>
-      <c r="U21" t="n">
-        <v>18</v>
-      </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="W21" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="Y21" t="n">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="Z21" t="n">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.534</v>
+        <v>0.543</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.333</v>
+        <v>0.214</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AK21" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.452</v>
+        <v>0.314</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>183.2</v>
+        <v>456.04</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.547</v>
+        <v>0.489</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.61</v>
+        <v>0.542</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.021</v>
+        <v>0.91</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.164</v>
+        <v>0.16</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.357</v>
+        <v>0.315</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.3</v>
+        <v>4.397</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.4</v>
+        <v>5.507</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.144</v>
+        <v>0.127</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3739,159 +3739,159 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>165</v>
+        <v>406</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E22" t="n">
+        <v>184</v>
+      </c>
+      <c r="F22" t="n">
+        <v>41</v>
+      </c>
+      <c r="G22" t="n">
+        <v>143</v>
+      </c>
+      <c r="H22" t="n">
+        <v>109</v>
+      </c>
+      <c r="I22" t="n">
+        <v>143</v>
+      </c>
+      <c r="J22" t="n">
+        <v>83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>140</v>
+      </c>
+      <c r="L22" t="n">
+        <v>77</v>
+      </c>
+      <c r="M22" t="n">
+        <v>38</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>16</v>
+      </c>
+      <c r="P22" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>32</v>
+      </c>
+      <c r="R22" t="n">
+        <v>126</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>264</v>
+      </c>
+      <c r="U22" t="n">
+        <v>46</v>
+      </c>
+      <c r="V22" t="n">
+        <v>46</v>
+      </c>
+      <c r="W22" t="n">
         <v>71</v>
       </c>
-      <c r="F22" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" t="n">
-        <v>55</v>
-      </c>
-      <c r="H22" t="n">
-        <v>50</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="X22" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y22" t="n">
         <v>67</v>
       </c>
-      <c r="J22" t="n">
-        <v>28</v>
-      </c>
-      <c r="K22" t="n">
-        <v>53</v>
-      </c>
-      <c r="L22" t="n">
-        <v>22</v>
-      </c>
-      <c r="M22" t="n">
-        <v>13</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>7</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Z22" t="n">
+        <v>136</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>51</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AK22" t="n">
         <v>29</v>
       </c>
-      <c r="Q22" t="n">
-        <v>10</v>
-      </c>
-      <c r="R22" t="n">
-        <v>52</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>102</v>
-      </c>
-      <c r="U22" t="n">
-        <v>27</v>
-      </c>
-      <c r="V22" t="n">
-        <v>23</v>
-      </c>
-      <c r="W22" t="n">
-        <v>26</v>
-      </c>
-      <c r="X22" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>10</v>
-      </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.312</v>
+        <v>0.315</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>184.48</v>
+        <v>473.92</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.531</v>
+        <v>0.521</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.894</v>
+        <v>0.857</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.157</v>
+        <v>0.177</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.397</v>
+        <v>0.333</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.966</v>
+        <v>0.988</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.345</v>
+        <v>3.893</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.31</v>
+        <v>4.881</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.056</v>
+        <v>0.073</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -4128,82 +4128,82 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="C25" t="n">
-        <v>18</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>78</v>
+      </c>
+      <c r="U25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>38</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X25" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0.792</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4218,72 +4218,72 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK25" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AL25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>31:04</t>
+          <t>28:57</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>11.82</v>
+        <v>13.16</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.789</v>
+        <v>0.68</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.832</v>
+        <v>0.714</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.523</v>
+        <v>1.277</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.316</v>
+        <v>0.32</v>
       </c>
       <c r="AU25" t="n">
-        <v>2</v>
+        <v>1.571</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.5</v>
+        <v>7.143</v>
       </c>
       <c r="AW25" t="n">
-        <v>11.5</v>
+        <v>8.714</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.166</v>
+        <v>0.199</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.149</v>
+        <v>0.13</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.082</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="26">
@@ -4293,97 +4293,97 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="C26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="M26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.5</v>
       </c>
-      <c r="M26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>14</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1</v>
-      </c>
       <c r="AE26" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AG26" t="n">
         <v>0.5</v>
@@ -4392,63 +4392,63 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AL26" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>27:44</t>
+          <t>24:22</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>13.88</v>
+        <v>10.104</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.556</v>
+        <v>0.431</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.607</v>
+        <v>0.493</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.865</v>
+        <v>0.772</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.288</v>
+        <v>0.218</v>
       </c>
       <c r="AT26" t="n">
         <v>0.222</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.75</v>
+        <v>1.727</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.25</v>
+        <v>3.273</v>
       </c>
       <c r="AW26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.218</v>
+        <v>0.182</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.019</v>
+        <v>0.042</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.037</v>
+        <v>0.062</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.115</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="27">
@@ -4458,88 +4458,88 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="n">
-        <v>12</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>9</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="M27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>31</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y27" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>16</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>3.5</v>
-      </c>
       <c r="Z27" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.467</v>
+        <v>0.455</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -4566,54 +4566,54 @@
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>15.08</v>
+        <v>12.328</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.333</v>
+        <v>0.349</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.442</v>
+        <v>0.424</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.796</v>
+        <v>0.779</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.099</v>
+        <v>0.081</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.476</v>
+        <v>0.419</v>
       </c>
       <c r="AU27" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.311</v>
+        <v>0.29</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.076</v>
+        <v>0.109</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.266</v>
+        <v>0.212</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.111</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="28">
@@ -4623,162 +4623,162 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D28" t="n">
         <v>2</v>
       </c>
-      <c r="C28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.5</v>
-      </c>
       <c r="E28" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="F28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>33</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AO28" t="n">
+        <v>5.776</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AU28" t="n">
         <v>0.5</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>19</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1</v>
-      </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>3.667</v>
       </c>
       <c r="AW28" t="n">
-        <v>13</v>
+        <v>4.167</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.183</v>
+        <v>0.152</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.209</v>
+        <v>0.17</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.264</v>
+        <v>0.181</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="29">
@@ -4788,43 +4788,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E29" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4833,43 +4833,43 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.429</v>
+        <v>0.632</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -4896,54 +4896,54 @@
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AM29" t="n">
         <v>0</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>5.22</v>
+        <v>6.392</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.375</v>
+        <v>0.522</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.415</v>
+        <v>0.575</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.67</v>
+        <v>0.97</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.192</v>
+        <v>0.156</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.125</v>
+        <v>0.304</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.12</v>
+        <v>0.138</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.162</v>
+        <v>0.158</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -4953,162 +4953,162 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H30" t="n">
         <v>1</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>20</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AM30" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>3.88</v>
+        <v>5.84</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.167</v>
+        <v>0.575</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.155</v>
+        <v>0.631</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.418</v>
+        <v>0.959</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.387</v>
+        <v>0.24</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.333</v>
+        <v>0.25</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AV30" t="n">
-        <v>1</v>
+        <v>2.857</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.333</v>
+        <v>3.286</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.126</v>
+        <v>0.147</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.038</v>
+        <v>0.119</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="31">
@@ -5118,162 +5118,162 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="C31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>0.5</v>
       </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="AK31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AP31" t="n">
         <v>0.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="AQ31" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AU31" t="n">
         <v>0.5</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>7</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.245</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AV31" t="n">
-        <v>2.333</v>
+        <v>3.75</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.667</v>
+        <v>4.25</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.205</v>
+        <v>0.174</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.049</v>
+        <v>0.019</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="32">
@@ -5283,92 +5283,92 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G32" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y32" t="n">
         <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD32" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
@@ -5382,63 +5382,63 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AL32" t="n">
         <v>1</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>4.44</v>
+        <v>6.104</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5</v>
+        <v>0.395</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.444</v>
+        <v>0.422</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.788</v>
+        <v>0.623</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.113</v>
+        <v>0.262</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="AU32" t="n">
-        <v>4</v>
+        <v>1.125</v>
       </c>
       <c r="AV32" t="n">
-        <v>7</v>
+        <v>2.375</v>
       </c>
       <c r="AW32" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.168</v>
+        <v>0.176</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.044</v>
+        <v>0.074</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="33">
@@ -5448,162 +5448,162 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="J33" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K33" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="L33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>22</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V33" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>14</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
       <c r="W33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI33" t="n">
         <v>2</v>
       </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA33" t="n">
+      <c r="AJ33" t="n">
         <v>0.3</v>
       </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AK33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AL33" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>25:04</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>14.08</v>
+        <v>14.064</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.316</v>
+        <v>0.385</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.477</v>
+        <v>0.456</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.852</v>
+        <v>0.782</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.107</v>
+        <v>0.142</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.632</v>
+        <v>0.375</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.333</v>
+        <v>4.8</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.333</v>
+        <v>5.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.245</v>
+        <v>0.264</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.043</v>
+        <v>0.061</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.102</v>
+        <v>0.073</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="34">
@@ -5778,91 +5778,91 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="D35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E35" t="n">
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I35" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K35" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="R35" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Z35" t="n">
         <v>5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AC35" t="n">
         <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -5877,63 +5877,63 @@
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AL35" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>0.364</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>24:15</t>
+          <t>24:16</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>11.48</v>
+        <v>12.8</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.667</v>
+        <v>0.533</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.738</v>
+        <v>0.616</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.22</v>
+        <v>1.078</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.174</v>
+        <v>0.125</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.533</v>
+        <v>0.467</v>
       </c>
       <c r="AU35" t="n">
         <v>0.75</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.75</v>
+        <v>5.625</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.5</v>
+        <v>6.375</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.207</v>
+        <v>0.231</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.19</v>
+        <v>0.117</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.058</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="36">
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -5970,10 +5970,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5985,10 +5985,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -6108,118 +6108,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>93.5</v>
+        <v>83</v>
       </c>
       <c r="D37" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="E37" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="F37" t="n">
-        <v>9.5</v>
+        <v>6.8</v>
       </c>
       <c r="G37" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="H37" t="n">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="I37" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="J37" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="K37" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L37" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="M37" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="R37" t="n">
-        <v>25.5</v>
+        <v>23.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>156</v>
+        <v>326</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="V37" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="W37" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="X37" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.5</v>
+        <v>20.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>36.5</v>
+        <v>37.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.534</v>
+        <v>0.543</v>
       </c>
       <c r="AB37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1</v>
       </c>
-      <c r="AC37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2</v>
-      </c>
       <c r="AG37" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI37" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AK37" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AL37" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.452</v>
+        <v>0.314</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6227,40 +6227,40 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>91.59999999999999</v>
+        <v>91.208</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.547</v>
+        <v>0.489</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.61</v>
+        <v>0.542</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.021</v>
+        <v>0.91</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.164</v>
+        <v>0.16</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.357</v>
+        <v>0.315</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.3</v>
+        <v>4.397</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.4</v>
+        <v>5.507</v>
       </c>
       <c r="AX37" t="n">
         <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.144</v>
+        <v>0.127</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6273,118 +6273,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>82.5</v>
+        <v>81.2</v>
       </c>
       <c r="D38" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="E38" t="n">
-        <v>35.5</v>
+        <v>36.8</v>
       </c>
       <c r="F38" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
       <c r="H38" t="n">
-        <v>25</v>
+        <v>21.8</v>
       </c>
       <c r="I38" t="n">
-        <v>33.5</v>
+        <v>28.6</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>16.6</v>
       </c>
       <c r="K38" t="n">
-        <v>26.5</v>
+        <v>28</v>
       </c>
       <c r="L38" t="n">
-        <v>11</v>
+        <v>15.4</v>
       </c>
       <c r="M38" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>14.5</v>
+        <v>16.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="R38" t="n">
-        <v>26</v>
+        <v>25.2</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="U38" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V38" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="X38" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>25.5</v>
+        <v>27.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.529</v>
+        <v>0.493</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.143</v>
+        <v>0.381</v>
       </c>
       <c r="AE38" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.538</v>
+        <v>0.444</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI38" t="n">
-        <v>11.5</v>
+        <v>10.2</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.217</v>
+        <v>0.235</v>
       </c>
       <c r="AK38" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AL38" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.312</v>
+        <v>0.315</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6392,40 +6392,40 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>92.23999999999999</v>
+        <v>94.78400000000001</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.531</v>
+        <v>0.521</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.894</v>
+        <v>0.857</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.157</v>
+        <v>0.177</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.397</v>
+        <v>0.333</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.966</v>
+        <v>0.988</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.345</v>
+        <v>3.893</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.31</v>
+        <v>4.881</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.201</v>
+        <v>0.208</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.059</v>
+        <v>0.078</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
